--- a/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007</t>
+          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47476</t>
+          <t>47449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79134</t>
+          <t>80491</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59740</t>
+          <t>59989</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>94056</t>
+          <t>97079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>115265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>163754</t>
+          <t>164519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>948457</t>
+          <t>947100</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>980115</t>
+          <t>980142</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1218309</t>
+          <t>1215286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1252625</t>
+          <t>1252376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2176202</t>
+          <t>2175437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2224027</t>
+          <t>2224691</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58837</t>
+          <t>59711</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93770</t>
+          <t>93651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83295</t>
+          <t>80952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>121106</t>
+          <t>122142</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152199</t>
+          <t>151758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205380</t>
+          <t>205899</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1593353</t>
+          <t>1593472</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1628286</t>
+          <t>1627412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1461419</t>
+          <t>1460383</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1499230</t>
+          <t>1501573</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3064269</t>
+          <t>3063750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3117450</t>
+          <t>3117891</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>12841</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31524</t>
+          <t>32016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16177</t>
+          <t>15331</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34913</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31911</t>
+          <t>31427</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60276</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519884</t>
+          <t>519392</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>539175</t>
+          <t>538567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440479</t>
+          <t>440334</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>459215</t>
+          <t>460061</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>966524</t>
+          <t>968571</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>994889</t>
+          <t>995373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132020</t>
+          <t>133944</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183004</t>
+          <t>187136</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>174184</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>232663</t>
+          <t>231291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>322844</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>400050</t>
+          <t>399602</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3083118</t>
+          <t>3078986</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3134102</t>
+          <t>3132178</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3137619</t>
+          <t>3138991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3196098</t>
+          <t>3196962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6236354</t>
+          <t>6236802</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6313560</t>
+          <t>6313260</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,13%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012</t>
+          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>39781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67987</t>
+          <t>67380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55188</t>
+          <t>55290</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88112</t>
+          <t>86813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102280</t>
+          <t>101159</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146236</t>
+          <t>145652</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>901523</t>
+          <t>902130</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>930633</t>
+          <t>929729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1244314</t>
+          <t>1245613</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1277238</t>
+          <t>1277136</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2155700</t>
+          <t>2156284</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2199656</t>
+          <t>2200777</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86791</t>
+          <t>85617</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128879</t>
+          <t>127629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>104889</t>
+          <t>105096</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148541</t>
+          <t>148030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>201288</t>
+          <t>204142</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>261082</t>
+          <t>260680</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1827552</t>
+          <t>1828802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1869640</t>
+          <t>1870814</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1601112</t>
+          <t>1601623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1644764</t>
+          <t>1644557</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3445002</t>
+          <t>3445404</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3504796</t>
+          <t>3501942</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1776</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11550</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15531</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>37403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20330</t>
+          <t>20383</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469631</t>
+          <t>469911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479338</t>
+          <t>479405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421756</t>
+          <t>421228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>442996</t>
+          <t>443100</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>895995</t>
+          <t>896879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>919483</t>
+          <t>919430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>137511</t>
+          <t>136971</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189449</t>
+          <t>189838</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>192769</t>
+          <t>190728</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>252109</t>
+          <t>249075</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>343387</t>
+          <t>342939</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>424303</t>
+          <t>421250</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3217674</t>
+          <t>3217285</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3269612</t>
+          <t>3270152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3288601</t>
+          <t>3291635</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3347941</t>
+          <t>3349982</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6523530</t>
+          <t>6526583</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6604446</t>
+          <t>6604894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016</t>
+          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26448</t>
+          <t>25916</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50532</t>
+          <t>47740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38711</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67828</t>
+          <t>66677</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72909</t>
+          <t>72288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108109</t>
+          <t>109179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>698325</t>
+          <t>701117</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>722409</t>
+          <t>722941</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>921489</t>
+          <t>922640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>950606</t>
+          <t>950352</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1630065</t>
+          <t>1628995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1665265</t>
+          <t>1665886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72116</t>
+          <t>70154</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109717</t>
+          <t>109837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,7 +4297,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>63859</t>
+          <t>62278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98664</t>
+          <t>98628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>146341</t>
+          <t>144096</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198015</t>
+          <t>198913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1957710</t>
+          <t>1957590</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1995311</t>
+          <t>1997273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1879516</t>
+          <t>1879552</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1914321</t>
+          <t>1915902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3847591</t>
+          <t>3846693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3899265</t>
+          <t>3901510</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12054</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28608</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18691</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40515</t>
+          <t>40535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>35002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>62775</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513380</t>
+          <t>512754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>529934</t>
+          <t>530207</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505758</t>
+          <t>505738</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527847</t>
+          <t>527582</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1024523</t>
+          <t>1025486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053027</t>
+          <t>1053259</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>123278</t>
+          <t>124591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>170536</t>
+          <t>172369</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136262</t>
+          <t>137007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>186503</t>
+          <t>188340</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>270605</t>
+          <t>271587</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341321</t>
+          <t>342266</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3187736</t>
+          <t>3185903</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3234994</t>
+          <t>3233681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3327267</t>
+          <t>3325430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3377508</t>
+          <t>3376763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6530721</t>
+          <t>6529776</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6601437</t>
+          <t>6600455</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023</t>
+          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>7941</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>22346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11638</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27707</t>
+          <t>27465</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23117</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41888</t>
+          <t>42277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489759</t>
+          <t>489554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503865</t>
+          <t>503959</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>716128</t>
+          <t>716370</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>732197</t>
+          <t>732338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213847</t>
+          <t>1213458</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1232618</t>
+          <t>1233081</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,2%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31465</t>
+          <t>31861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73095</t>
+          <t>71967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>43270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82941</t>
+          <t>84628</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,47 +5935,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>3,81%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>112384</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>86175</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>140962</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>2,5%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>1,92%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,73%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>112384</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>85049</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>144076</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2201009</t>
+          <t>2202137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2242639</t>
+          <t>2242243</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2140818</t>
+          <t>2139131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2181095</t>
+          <t>2180489</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,47 +6048,47 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>98,05%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>4736</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>4385480</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>4356902</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4411689</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>97,5%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>98,08%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>4736</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>4385480</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>4353788</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4412815</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6452</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22025</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21187</t>
+          <t>21035</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616366</t>
+          <t>616703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632276</t>
+          <t>632218</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630974</t>
+          <t>631126</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645373</t>
+          <t>645872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1254580</t>
+          <t>1255324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275356</t>
+          <t>1275404</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56641</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100759</t>
+          <t>101048</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71419</t>
+          <t>69298</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>113594</t>
+          <t>115898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,47 +6621,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>167518</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>138810</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>202166</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>1,97%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>167518</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>138562</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>200697</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3323973</t>
+          <t>3323684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3368091</t>
+          <t>3370857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3506162</t>
+          <t>3503858</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3548337</t>
+          <t>3550458</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6843791</t>
+          <t>6842322</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6905926</t>
+          <t>6905678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47449</t>
+          <t>47944</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80491</t>
+          <t>78598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>59989</t>
+          <t>60441</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>97079</t>
+          <t>95320</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>117080</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>164519</t>
+          <t>163089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>947100</t>
+          <t>948993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>980142</t>
+          <t>979647</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1215286</t>
+          <t>1217045</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1252376</t>
+          <t>1251924</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2175437</t>
+          <t>2176867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2224691</t>
+          <t>2222876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59711</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93651</t>
+          <t>94328</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122142</t>
+          <t>123607</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151758</t>
+          <t>152958</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205899</t>
+          <t>207885</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1593472</t>
+          <t>1592795</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1627412</t>
+          <t>1627664</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1460383</t>
+          <t>1458918</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1501573</t>
+          <t>1499652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3063750</t>
+          <t>3061764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3117891</t>
+          <t>3116691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12841</t>
+          <t>12661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32016</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15331</t>
+          <t>15681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>35539</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>31560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58229</t>
+          <t>58863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519392</t>
+          <t>519193</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>538567</t>
+          <t>538747</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>440334</t>
+          <t>439853</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>460061</t>
+          <t>459711</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>968571</t>
+          <t>967937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>995373</t>
+          <t>995240</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133944</t>
+          <t>133114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187136</t>
+          <t>185742</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173320</t>
+          <t>174603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>231291</t>
+          <t>230064</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>323144</t>
+          <t>319328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>399602</t>
+          <t>394110</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3078986</t>
+          <t>3080380</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3132178</t>
+          <t>3133008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3138991</t>
+          <t>3140218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3196962</t>
+          <t>3195679</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6236802</t>
+          <t>6242294</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6313260</t>
+          <t>6317076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,19%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39781</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67380</t>
+          <t>67611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55290</t>
+          <t>55250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86813</t>
+          <t>88709</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101159</t>
+          <t>102853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145652</t>
+          <t>144742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>902130</t>
+          <t>901899</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>929729</t>
+          <t>930400</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1245613</t>
+          <t>1243717</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1277136</t>
+          <t>1277176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2156284</t>
+          <t>2157194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2200777</t>
+          <t>2199083</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85617</t>
+          <t>82811</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127629</t>
+          <t>126041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105096</t>
+          <t>103630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>148030</t>
+          <t>149170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>204142</t>
+          <t>201814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260680</t>
+          <t>266163</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1828802</t>
+          <t>1830390</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1870814</t>
+          <t>1873620</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1601623</t>
+          <t>1600483</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1644557</t>
+          <t>1646023</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3445404</t>
+          <t>3439921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3501942</t>
+          <t>3504270</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11270</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15531</t>
+          <t>16067</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37403</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>20158</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469911</t>
+          <t>469856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479405</t>
+          <t>479563</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421228</t>
+          <t>421991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443100</t>
+          <t>442564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>896879</t>
+          <t>897462</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>919430</t>
+          <t>919655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,86%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>136971</t>
+          <t>139567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189838</t>
+          <t>191169</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>190728</t>
+          <t>190686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249075</t>
+          <t>251924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342939</t>
+          <t>341918</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>421250</t>
+          <t>419828</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3217285</t>
+          <t>3215954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3270152</t>
+          <t>3267556</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3291635</t>
+          <t>3288786</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3349982</t>
+          <t>3350024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6526583</t>
+          <t>6528005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6604894</t>
+          <t>6605915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,08%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25916</t>
+          <t>25805</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47740</t>
+          <t>50731</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>40244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66677</t>
+          <t>68390</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72288</t>
+          <t>72369</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>109179</t>
+          <t>109911</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>701117</t>
+          <t>698126</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>722941</t>
+          <t>723052</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>922640</t>
+          <t>920927</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>950352</t>
+          <t>949073</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1628995</t>
+          <t>1628263</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1665886</t>
+          <t>1665805</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>70402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>109837</t>
+          <t>110980</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62278</t>
+          <t>64592</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98628</t>
+          <t>101050</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144096</t>
+          <t>143418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>198913</t>
+          <t>196280</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1957590</t>
+          <t>1956447</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1997273</t>
+          <t>1997025</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1879552</t>
+          <t>1877130</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1915902</t>
+          <t>1913588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3846693</t>
+          <t>3849326</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3901510</t>
+          <t>3902188</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,45%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>29719</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18691</t>
+          <t>18937</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40535</t>
+          <t>41011</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35002</t>
+          <t>34325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62775</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>512754</t>
+          <t>512269</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>530207</t>
+          <t>530551</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>505738</t>
+          <t>505262</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>527582</t>
+          <t>527336</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1025486</t>
+          <t>1027015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1053259</t>
+          <t>1053936</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,85%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124591</t>
+          <t>122309</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172369</t>
+          <t>170925</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137007</t>
+          <t>135695</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>188340</t>
+          <t>186085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>271587</t>
+          <t>270235</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>342266</t>
+          <t>336915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3185903</t>
+          <t>3187347</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3233681</t>
+          <t>3235963</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3325430</t>
+          <t>3327685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3376763</t>
+          <t>3378075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6529776</t>
+          <t>6535127</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6600455</t>
+          <t>6601807</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17691</t>
+          <t>21028</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11497</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27465</t>
+          <t>30029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>31357</t>
+          <t>40043</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22654</t>
+          <t>29835</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42277</t>
+          <t>53133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>498234</t>
+          <t>556576</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489554</t>
+          <t>546815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>503959</t>
+          <t>563529</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>726144</t>
+          <t>789840</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>716370</t>
+          <t>780839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>732338</t>
+          <t>796837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1224378</t>
+          <t>1346416</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1213458</t>
+          <t>1333326</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1233081</t>
+          <t>1356624</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>511900</t>
+          <t>575591</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>511900</t>
+          <t>575591</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>511900</t>
+          <t>575591</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>743835</t>
+          <t>810868</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>743835</t>
+          <t>810868</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>743835</t>
+          <t>810868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1255735</t>
+          <t>1386459</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1255735</t>
+          <t>1386459</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1255735</t>
+          <t>1386459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>60298</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>43738</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71967</t>
+          <t>80656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>61405</t>
+          <t>80811</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>64806</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>84628</t>
+          <t>101482</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>112384</t>
+          <t>141109</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86175</t>
+          <t>117517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140962</t>
+          <t>168721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2223125</t>
+          <t>2153327</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2202137</t>
+          <t>2132969</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2242243</t>
+          <t>2169887</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2162354</t>
+          <t>2074467</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2139131</t>
+          <t>2053796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2180489</t>
+          <t>2090472</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4385480</t>
+          <t>4227794</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4356902</t>
+          <t>4200182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4411689</t>
+          <t>4251386</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>97,31%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2274104</t>
+          <t>2213625</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2274104</t>
+          <t>2213625</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2274104</t>
+          <t>2213625</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2223759</t>
+          <t>2155278</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2223759</t>
+          <t>2155278</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2223759</t>
+          <t>2155278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4497864</t>
+          <t>4368903</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4497864</t>
+          <t>4368903</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4497864</t>
+          <t>4368903</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>15716</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>26410</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11890</t>
+          <t>18772</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>29829</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>34488</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>23843</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>626841</t>
+          <t>687738</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>616703</t>
+          <t>677044</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632218</t>
+          <t>694619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>640271</t>
+          <t>706719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631126</t>
+          <t>695662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>645872</t>
+          <t>714129</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1267112</t>
+          <t>1394457</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1255324</t>
+          <t>1380599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1275404</t>
+          <t>1405102</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,33%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>638728</t>
+          <t>703454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>638728</t>
+          <t>703454</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>638728</t>
+          <t>703454</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>652161</t>
+          <t>725491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>652161</t>
+          <t>725491</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>652161</t>
+          <t>725491</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1290889</t>
+          <t>1428945</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1290889</t>
+          <t>1428945</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1290889</t>
+          <t>1428945</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>76532</t>
+          <t>95029</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53875</t>
+          <t>74600</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101048</t>
+          <t>118339</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69298</t>
+          <t>102084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>115898</t>
+          <t>142991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>167518</t>
+          <t>215640</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138810</t>
+          <t>187710</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>202166</t>
+          <t>247940</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3348200</t>
+          <t>3397640</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3323684</t>
+          <t>3374330</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3370857</t>
+          <t>3418069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3528770</t>
+          <t>3571026</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3503858</t>
+          <t>3548646</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3550458</t>
+          <t>3589553</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6876970</t>
+          <t>6968666</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6842322</t>
+          <t>6936366</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6905678</t>
+          <t>6996596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3424732</t>
+          <t>3492669</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3424732</t>
+          <t>3492669</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3424732</t>
+          <t>3492669</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3619756</t>
+          <t>3691637</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3619756</t>
+          <t>3691637</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3619756</t>
+          <t>3691637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7044488</t>
+          <t>7184306</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7044488</t>
+          <t>7184306</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7044488</t>
+          <t>7184306</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2012 (tasa de respuesta: 99,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2016 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
+          <t>Población según si en su vivienda residen dos o más personas por habitación en 2023 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
